--- a/ExportExcel/Delete Majors Test.xlsx
+++ b/ExportExcel/Delete Majors Test.xlsx
@@ -41,7 +41,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>1927 ms</t>
+    <t>1486 ms</t>
   </si>
   <si>
     <t/>
@@ -53,7 +53,7 @@
     <t>TC_DM_02</t>
   </si>
   <si>
-    <t>4693 ms</t>
+    <t>2281 ms</t>
   </si>
 </sst>
 </file>
